--- a/artfynd/A 11352-2022 artfynd.xlsx
+++ b/artfynd/A 11352-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132261031</v>
       </c>
       <c r="B2" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132260778</v>
       </c>
       <c r="B3" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132263145</v>
+        <v>132264816</v>
       </c>
       <c r="B4" t="n">
-        <v>58107</v>
+        <v>91892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620949</v>
+        <v>620795</v>
       </c>
       <c r="R4" t="n">
-        <v>6917266</v>
+        <v>6917395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,45 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132261019</v>
+        <v>132263145</v>
       </c>
       <c r="B5" t="n">
-        <v>99095</v>
+        <v>58109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620816</v>
+        <v>620949</v>
       </c>
       <c r="R5" t="n">
-        <v>6917388</v>
+        <v>6917266</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132264816</v>
+        <v>132261019</v>
       </c>
       <c r="B6" t="n">
-        <v>91889</v>
+        <v>99098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620795</v>
+        <v>620816</v>
       </c>
       <c r="R6" t="n">
-        <v>6917395</v>
+        <v>6917388</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>132263768</v>
       </c>
       <c r="B7" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>132260617</v>
       </c>
       <c r="B8" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>132263887</v>
       </c>
       <c r="B9" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>132264217</v>
       </c>
       <c r="B10" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>132267057</v>
       </c>
       <c r="B11" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>132261120</v>
       </c>
       <c r="B12" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>132266833</v>
       </c>
       <c r="B13" t="n">
-        <v>58629</v>
+        <v>58631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11352-2022 artfynd.xlsx
+++ b/artfynd/A 11352-2022 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132264816</v>
+        <v>132263145</v>
       </c>
       <c r="B4" t="n">
-        <v>91892</v>
+        <v>58109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620795</v>
+        <v>620949</v>
       </c>
       <c r="R4" t="n">
-        <v>6917395</v>
+        <v>6917266</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132263145</v>
+        <v>132264816</v>
       </c>
       <c r="B5" t="n">
-        <v>58109</v>
+        <v>91892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620949</v>
+        <v>620795</v>
       </c>
       <c r="R5" t="n">
-        <v>6917266</v>
+        <v>6917395</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 11352-2022 artfynd.xlsx
+++ b/artfynd/A 11352-2022 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132263145</v>
+        <v>132264816</v>
       </c>
       <c r="B4" t="n">
-        <v>58109</v>
+        <v>91892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620949</v>
+        <v>620795</v>
       </c>
       <c r="R4" t="n">
-        <v>6917266</v>
+        <v>6917395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132264816</v>
+        <v>132263145</v>
       </c>
       <c r="B5" t="n">
-        <v>91892</v>
+        <v>58109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620795</v>
+        <v>620949</v>
       </c>
       <c r="R5" t="n">
-        <v>6917395</v>
+        <v>6917266</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 11352-2022 artfynd.xlsx
+++ b/artfynd/A 11352-2022 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132264816</v>
+        <v>132263145</v>
       </c>
       <c r="B4" t="n">
-        <v>91892</v>
+        <v>58109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620795</v>
+        <v>620949</v>
       </c>
       <c r="R4" t="n">
-        <v>6917395</v>
+        <v>6917266</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,45 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132263145</v>
+        <v>132261019</v>
       </c>
       <c r="B5" t="n">
-        <v>58109</v>
+        <v>99098</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620949</v>
+        <v>620816</v>
       </c>
       <c r="R5" t="n">
-        <v>6917266</v>
+        <v>6917388</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132261019</v>
+        <v>132264816</v>
       </c>
       <c r="B6" t="n">
-        <v>99098</v>
+        <v>91892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620816</v>
+        <v>620795</v>
       </c>
       <c r="R6" t="n">
-        <v>6917388</v>
+        <v>6917395</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1354,45 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132263887</v>
+        <v>132264217</v>
       </c>
       <c r="B9" t="n">
-        <v>58322</v>
+        <v>99098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620928</v>
+        <v>620856</v>
       </c>
       <c r="R9" t="n">
-        <v>6917275</v>
+        <v>6917353</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,45 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132264217</v>
+        <v>132263887</v>
       </c>
       <c r="B10" t="n">
-        <v>99098</v>
+        <v>58322</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620856</v>
+        <v>620928</v>
       </c>
       <c r="R10" t="n">
-        <v>6917353</v>
+        <v>6917275</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 11352-2022 artfynd.xlsx
+++ b/artfynd/A 11352-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132261031</v>
       </c>
       <c r="B2" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132260778</v>
       </c>
       <c r="B3" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,45 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132263145</v>
+        <v>132261019</v>
       </c>
       <c r="B4" t="n">
-        <v>58109</v>
+        <v>99106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620949</v>
+        <v>620816</v>
       </c>
       <c r="R4" t="n">
-        <v>6917266</v>
+        <v>6917388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132261019</v>
+        <v>132264816</v>
       </c>
       <c r="B5" t="n">
-        <v>99098</v>
+        <v>91898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620816</v>
+        <v>620795</v>
       </c>
       <c r="R5" t="n">
-        <v>6917388</v>
+        <v>6917395</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132264816</v>
+        <v>132263145</v>
       </c>
       <c r="B6" t="n">
-        <v>91892</v>
+        <v>58110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620795</v>
+        <v>620949</v>
       </c>
       <c r="R6" t="n">
-        <v>6917395</v>
+        <v>6917266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>132263768</v>
       </c>
       <c r="B7" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>132260617</v>
       </c>
       <c r="B8" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,45 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132264217</v>
+        <v>132263887</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>58323</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620856</v>
+        <v>620928</v>
       </c>
       <c r="R9" t="n">
-        <v>6917353</v>
+        <v>6917275</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,45 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132263887</v>
+        <v>132264217</v>
       </c>
       <c r="B10" t="n">
-        <v>58322</v>
+        <v>99106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620928</v>
+        <v>620856</v>
       </c>
       <c r="R10" t="n">
-        <v>6917275</v>
+        <v>6917353</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>132267057</v>
       </c>
       <c r="B11" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>132261120</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>132266833</v>
       </c>
       <c r="B13" t="n">
-        <v>58631</v>
+        <v>58632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11352-2022 artfynd.xlsx
+++ b/artfynd/A 11352-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132261031</v>
       </c>
       <c r="B2" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132260778</v>
       </c>
       <c r="B3" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,45 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132261019</v>
+        <v>132263145</v>
       </c>
       <c r="B4" t="n">
-        <v>99106</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620816</v>
+        <v>620949</v>
       </c>
       <c r="R4" t="n">
-        <v>6917388</v>
+        <v>6917266</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>132264816</v>
       </c>
       <c r="B5" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,45 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132263145</v>
+        <v>132261019</v>
       </c>
       <c r="B6" t="n">
-        <v>58110</v>
+        <v>99116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620949</v>
+        <v>620816</v>
       </c>
       <c r="R6" t="n">
-        <v>6917266</v>
+        <v>6917388</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>132263768</v>
       </c>
       <c r="B7" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>132260617</v>
       </c>
       <c r="B8" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>132263887</v>
       </c>
       <c r="B9" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>132264217</v>
       </c>
       <c r="B10" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>132267057</v>
       </c>
       <c r="B11" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>132261120</v>
       </c>
       <c r="B12" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>132266833</v>
       </c>
       <c r="B13" t="n">
-        <v>58632</v>
+        <v>58636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11352-2022 artfynd.xlsx
+++ b/artfynd/A 11352-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>132260778</v>
       </c>
       <c r="B3" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132263145</v>
+        <v>132264816</v>
       </c>
       <c r="B4" t="n">
-        <v>58114</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620949</v>
+        <v>620795</v>
       </c>
       <c r="R4" t="n">
-        <v>6917266</v>
+        <v>6917395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132264816</v>
+        <v>132261019</v>
       </c>
       <c r="B5" t="n">
-        <v>91908</v>
+        <v>99117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620795</v>
+        <v>620816</v>
       </c>
       <c r="R5" t="n">
-        <v>6917395</v>
+        <v>6917388</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,45 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132261019</v>
+        <v>132263145</v>
       </c>
       <c r="B6" t="n">
-        <v>99116</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620816</v>
+        <v>620949</v>
       </c>
       <c r="R6" t="n">
-        <v>6917388</v>
+        <v>6917266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>132263768</v>
       </c>
       <c r="B7" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,45 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132263887</v>
+        <v>132264217</v>
       </c>
       <c r="B9" t="n">
-        <v>58327</v>
+        <v>99117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620928</v>
+        <v>620856</v>
       </c>
       <c r="R9" t="n">
-        <v>6917275</v>
+        <v>6917353</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,45 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132264217</v>
+        <v>132263887</v>
       </c>
       <c r="B10" t="n">
-        <v>99116</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620856</v>
+        <v>620928</v>
       </c>
       <c r="R10" t="n">
-        <v>6917353</v>
+        <v>6917275</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>132267057</v>
       </c>
       <c r="B11" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>132261120</v>
       </c>
       <c r="B12" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11352-2022 artfynd.xlsx
+++ b/artfynd/A 11352-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>132260778</v>
       </c>
       <c r="B3" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132264816</v>
+        <v>132261019</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620795</v>
+        <v>620816</v>
       </c>
       <c r="R4" t="n">
-        <v>6917395</v>
+        <v>6917388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132261019</v>
+        <v>132264816</v>
       </c>
       <c r="B5" t="n">
-        <v>99117</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620816</v>
+        <v>620795</v>
       </c>
       <c r="R5" t="n">
-        <v>6917388</v>
+        <v>6917395</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>132263768</v>
       </c>
       <c r="B7" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,45 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132264217</v>
+        <v>132263887</v>
       </c>
       <c r="B9" t="n">
-        <v>99117</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620856</v>
+        <v>620928</v>
       </c>
       <c r="R9" t="n">
-        <v>6917353</v>
+        <v>6917275</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,45 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132263887</v>
+        <v>132264217</v>
       </c>
       <c r="B10" t="n">
-        <v>58327</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620928</v>
+        <v>620856</v>
       </c>
       <c r="R10" t="n">
-        <v>6917275</v>
+        <v>6917353</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>132267057</v>
       </c>
       <c r="B11" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>132261120</v>
       </c>
       <c r="B12" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11352-2022 artfynd.xlsx
+++ b/artfynd/A 11352-2022 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132261019</v>
+        <v>132264816</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620816</v>
+        <v>620795</v>
       </c>
       <c r="R4" t="n">
-        <v>6917388</v>
+        <v>6917395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132264816</v>
+        <v>132261019</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620795</v>
+        <v>620816</v>
       </c>
       <c r="R5" t="n">
-        <v>6917395</v>
+        <v>6917388</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1354,45 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132263887</v>
+        <v>132264217</v>
       </c>
       <c r="B9" t="n">
-        <v>58327</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620928</v>
+        <v>620856</v>
       </c>
       <c r="R9" t="n">
-        <v>6917275</v>
+        <v>6917353</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,45 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132264217</v>
+        <v>132263887</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620856</v>
+        <v>620928</v>
       </c>
       <c r="R10" t="n">
-        <v>6917353</v>
+        <v>6917275</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 11352-2022 artfynd.xlsx
+++ b/artfynd/A 11352-2022 artfynd.xlsx
@@ -1354,45 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132264217</v>
+        <v>132263887</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620856</v>
+        <v>620928</v>
       </c>
       <c r="R9" t="n">
-        <v>6917353</v>
+        <v>6917275</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,45 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132263887</v>
+        <v>132264217</v>
       </c>
       <c r="B10" t="n">
-        <v>58327</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620928</v>
+        <v>620856</v>
       </c>
       <c r="R10" t="n">
-        <v>6917275</v>
+        <v>6917353</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 11352-2022 artfynd.xlsx
+++ b/artfynd/A 11352-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132261031</v>
       </c>
       <c r="B2" t="n">
-        <v>58327</v>
+        <v>58328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132260778</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132264816</v>
+        <v>132263145</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>58115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620795</v>
+        <v>620949</v>
       </c>
       <c r="R4" t="n">
-        <v>6917395</v>
+        <v>6917266</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>132261019</v>
       </c>
       <c r="B5" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132263145</v>
+        <v>132264816</v>
       </c>
       <c r="B6" t="n">
-        <v>58114</v>
+        <v>91910</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620949</v>
+        <v>620795</v>
       </c>
       <c r="R6" t="n">
-        <v>6917266</v>
+        <v>6917395</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>132263768</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>132260617</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>132263887</v>
       </c>
       <c r="B9" t="n">
-        <v>58327</v>
+        <v>58328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>132264217</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>132267057</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>132261120</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>132266833</v>
       </c>
       <c r="B13" t="n">
-        <v>58636</v>
+        <v>58637</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11352-2022 artfynd.xlsx
+++ b/artfynd/A 11352-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132261031</v>
+        <v>132264816</v>
       </c>
       <c r="B2" t="n">
-        <v>58328</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620802</v>
+        <v>620795</v>
       </c>
       <c r="R2" t="n">
-        <v>6917390</v>
+        <v>6917395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132260778</v>
+        <v>132260617</v>
       </c>
       <c r="B3" t="n">
-        <v>99122</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620730</v>
+        <v>620715</v>
       </c>
       <c r="R3" t="n">
-        <v>6917538</v>
+        <v>6917556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132264816</v>
+        <v>132259888</v>
       </c>
       <c r="B4" t="n">
-        <v>91913</v>
+        <v>57153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620795</v>
+        <v>620708</v>
       </c>
       <c r="R4" t="n">
-        <v>6917395</v>
+        <v>6917597</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,45 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132263145</v>
+        <v>132261031</v>
       </c>
       <c r="B5" t="n">
-        <v>58115</v>
+        <v>58349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620949</v>
+        <v>620802</v>
       </c>
       <c r="R5" t="n">
-        <v>6917266</v>
+        <v>6917390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,45 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132261019</v>
+        <v>132263887</v>
       </c>
       <c r="B6" t="n">
-        <v>99122</v>
+        <v>58349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620816</v>
+        <v>620928</v>
       </c>
       <c r="R6" t="n">
-        <v>6917388</v>
+        <v>6917275</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132263768</v>
+        <v>132260182</v>
       </c>
       <c r="B7" t="n">
-        <v>99122</v>
+        <v>58136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620942</v>
+        <v>620701</v>
       </c>
       <c r="R7" t="n">
-        <v>6917274</v>
+        <v>6917590</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132260617</v>
+        <v>132263145</v>
       </c>
       <c r="B8" t="n">
-        <v>79329</v>
+        <v>58136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hillstamon, Hillstamon, Mpd</t>
+          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620715</v>
+        <v>620949</v>
       </c>
       <c r="R8" t="n">
-        <v>6917556</v>
+        <v>6917266</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132263887</v>
+        <v>132266833</v>
       </c>
       <c r="B9" t="n">
-        <v>58328</v>
+        <v>58658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620928</v>
+        <v>620939</v>
       </c>
       <c r="R9" t="n">
-        <v>6917275</v>
+        <v>6917329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132264217</v>
+        <v>132260778</v>
       </c>
       <c r="B10" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620856</v>
+        <v>620730</v>
       </c>
       <c r="R10" t="n">
-        <v>6917353</v>
+        <v>6917538</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132267057</v>
+        <v>132261019</v>
       </c>
       <c r="B11" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621067</v>
+        <v>620816</v>
       </c>
       <c r="R11" t="n">
-        <v>6917397</v>
+        <v>6917388</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>132261120</v>
       </c>
       <c r="B12" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,45 +1742,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132266833</v>
+        <v>132263768</v>
       </c>
       <c r="B13" t="n">
-        <v>58637</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Amerika Svensson, Amerika Svensson, Mpd</t>
+          <t>Hillstamon, Hillstamon, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620939</v>
+        <v>620942</v>
       </c>
       <c r="R13" t="n">
-        <v>6917329</v>
+        <v>6917274</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1836,6 +1836,297 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132264217</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hillstamon, Hillstamon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>620856</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6917353</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132265034</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hillstamon, Hillstamon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>620774</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6917406</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132267057</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hillstamon, Hillstamon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>621067</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6917397</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11352-2022 artfynd.xlsx
+++ b/artfynd/A 11352-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132264816</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132260617</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132259888</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132261031</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132263887</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132260182</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132263145</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132266833</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132260778</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132261019</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132261120</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132263768</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132264217</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132265034</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,8 +2202,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132267057</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>